--- a/docs/reports/daily/NCR_Kavach_Unified_KPI_Jun30-Jun30.xlsx
+++ b/docs/reports/daily/NCR_Kavach_Unified_KPI_Jun30-Jun30.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,10 +22,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -207,13 +207,13 @@
     <xf numFmtId="3" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,7 +229,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -244,7 +244,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -259,7 +259,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -300,6 +300,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -705,7 +723,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -848,19 +865,19 @@
         <f>'Daily Breakdown'!J40</f>
         <v/>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="43">
         <f>IFERROR(G5/D5,0)</f>
         <v/>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="44">
         <f>IFERROR(G5/E5,0)</f>
         <v/>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="45">
         <f>IFERROR(G5/E5*100,0)</f>
         <v/>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="44">
         <f>IFERROR(G5/(D5*E5/1000),0)</f>
         <v/>
       </c>
@@ -868,19 +885,19 @@
         <f>'Daily Breakdown'!K40</f>
         <v/>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="43">
         <f>IFERROR(N5/D5,0)</f>
         <v/>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="44">
         <f>IFERROR(N5/E5,0)</f>
         <v/>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="44">
         <f>IFERROR(N5/(D5*E5/100),0)</f>
         <v/>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="45">
         <f>IFERROR(N5/E5*100,0)</f>
         <v/>
       </c>
@@ -930,7 +947,13 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="36" t="inlineStr">
+        <is>
+          <t>Availability base excludes locos with FS+OS pkts = 0 (they are still listed below; only the Total-pkts availability base drops them).</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1002,7 +1025,7 @@
       <c r="C4" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="46" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E4" s="18" t="n">
@@ -1042,7 +1065,7 @@
       <c r="C5" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="46" t="n">
         <v>77.87</v>
       </c>
       <c r="E5" s="18" t="n">
@@ -1082,7 +1105,7 @@
       <c r="C6" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="46" t="n">
         <v>77.86</v>
       </c>
       <c r="E6" s="18" t="n">
@@ -1122,7 +1145,7 @@
       <c r="C7" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="46" t="n">
         <v>77.88</v>
       </c>
       <c r="E7" s="18" t="n">
@@ -1162,7 +1185,7 @@
       <c r="C8" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="46" t="n">
         <v>77.86</v>
       </c>
       <c r="E8" s="18" t="n">
@@ -1202,7 +1225,7 @@
       <c r="C9" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="46" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E9" s="18" t="n">
@@ -1242,7 +1265,7 @@
       <c r="C10" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="46" t="n">
         <v>77.86</v>
       </c>
       <c r="E10" s="18" t="n">
@@ -1282,7 +1305,7 @@
       <c r="C11" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="46" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E11" s="18" t="n">
@@ -1322,7 +1345,7 @@
       <c r="C12" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="46" t="n">
         <v>77.86</v>
       </c>
       <c r="E12" s="18" t="n">
@@ -1362,7 +1385,7 @@
       <c r="C13" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="46" t="n">
         <v>77.84</v>
       </c>
       <c r="E13" s="18" t="n">
@@ -1402,7 +1425,7 @@
       <c r="C14" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="46" t="n">
         <v>77.73</v>
       </c>
       <c r="E14" s="18" t="n">
@@ -1442,7 +1465,7 @@
       <c r="C15" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="46" t="n">
         <v>77.73</v>
       </c>
       <c r="E15" s="18" t="n">
@@ -1482,7 +1505,7 @@
       <c r="C16" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="46" t="n">
         <v>77.67</v>
       </c>
       <c r="E16" s="18" t="n">
@@ -1522,7 +1545,7 @@
       <c r="C17" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="46" t="n">
         <v>77.87</v>
       </c>
       <c r="E17" s="18" t="n">
@@ -1562,7 +1585,7 @@
       <c r="C18" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="46" t="n">
         <v>77.84</v>
       </c>
       <c r="E18" s="18" t="n">
@@ -1602,7 +1625,7 @@
       <c r="C19" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="46" t="n">
         <v>77.73</v>
       </c>
       <c r="E19" s="18" t="n">
@@ -1642,7 +1665,7 @@
       <c r="C20" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="46" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E20" s="18" t="n">
@@ -1682,7 +1705,7 @@
       <c r="C21" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="46" t="n">
         <v>77.87</v>
       </c>
       <c r="E21" s="18" t="n">
@@ -1722,7 +1745,7 @@
       <c r="C22" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="46" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E22" s="18" t="n">
@@ -1762,7 +1785,7 @@
       <c r="C23" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="46" t="n">
         <v>77.68000000000001</v>
       </c>
       <c r="E23" s="18" t="n">
@@ -1802,7 +1825,7 @@
       <c r="C24" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="46" t="n">
         <v>77.83</v>
       </c>
       <c r="E24" s="18" t="n">
@@ -1842,7 +1865,7 @@
       <c r="C25" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="46" t="n">
         <v>77.87</v>
       </c>
       <c r="E25" s="18" t="n">
@@ -1882,7 +1905,7 @@
       <c r="C26" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="46" t="n">
         <v>77.69</v>
       </c>
       <c r="E26" s="18" t="n">
@@ -1922,7 +1945,7 @@
       <c r="C27" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="46" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E27" s="18" t="n">
@@ -1962,7 +1985,7 @@
       <c r="C28" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="46" t="n">
         <v>22.8</v>
       </c>
       <c r="E28" s="18" t="n">
@@ -2002,7 +2025,7 @@
       <c r="C29" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="46" t="n">
         <v>77.86</v>
       </c>
       <c r="E29" s="18" t="n">
@@ -2042,7 +2065,7 @@
       <c r="C30" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="46" t="n">
         <v>77.87</v>
       </c>
       <c r="E30" s="18" t="n">
@@ -2082,7 +2105,7 @@
       <c r="C31" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="46" t="n">
         <v>76.93000000000001</v>
       </c>
       <c r="E31" s="18" t="n">
@@ -2122,7 +2145,7 @@
       <c r="C32" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="46" t="n">
         <v>24.06</v>
       </c>
       <c r="E32" s="18" t="n">
@@ -2162,7 +2185,7 @@
       <c r="C33" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="46" t="n">
         <v>76.56999999999999</v>
       </c>
       <c r="E33" s="18" t="n">
@@ -2202,7 +2225,7 @@
       <c r="C34" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="46" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="18" t="n">
@@ -2242,7 +2265,7 @@
       <c r="C35" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="46" t="n">
         <v>11.9</v>
       </c>
       <c r="E35" s="18" t="n">
@@ -2282,7 +2305,7 @@
       <c r="C36" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="46" t="n">
         <v>9.08</v>
       </c>
       <c r="E36" s="18" t="n">
@@ -2322,7 +2345,7 @@
       <c r="C37" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="17" t="n">
+      <c r="D37" s="46" t="n">
         <v>12.85</v>
       </c>
       <c r="E37" s="18" t="n">
@@ -2362,7 +2385,7 @@
       <c r="C38" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="46" t="n">
         <v>17.83</v>
       </c>
       <c r="E38" s="18" t="n">
@@ -2403,7 +2426,7 @@
         <f>SUM(C4:C38)</f>
         <v/>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="47">
         <f>SUM(D4:D38)</f>
         <v/>
       </c>
@@ -2412,7 +2435,7 @@
         <v/>
       </c>
       <c r="F39" s="23">
-        <f>SUM(F4:F38)</f>
+        <f>SUMIF(E4:E38,"&gt;0",F4:F38)</f>
         <v/>
       </c>
       <c r="G39" s="24">
@@ -2447,7 +2470,7 @@
         <f>C39</f>
         <v/>
       </c>
-      <c r="D40" s="27">
+      <c r="D40" s="48">
         <f>D39</f>
         <v/>
       </c>
@@ -2523,7 +2546,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="30" t="inlineStr">
         <is>
@@ -2531,7 +2553,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -5660,7 +5681,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -7390,7 +7410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="B1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -7405,7 +7425,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="34" customHeight="1">
       <c r="B3" s="41" t="inlineStr">
         <is>

--- a/docs/reports/daily/NCR_Kavach_Unified_KPI_Jun30-Jun30.xlsx
+++ b/docs/reports/daily/NCR_Kavach_Unified_KPI_Jun30-Jun30.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2813,7 +2813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2891,6 +2891,11 @@
           <t>Valid Trip?</t>
         </is>
       </c>
+      <c r="M5" s="14" t="inlineStr">
+        <is>
+          <t>Loco Travel</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -2947,6 +2952,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M6" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -3003,6 +3013,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -3059,6 +3074,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M8" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -3115,6 +3135,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
@@ -3171,6 +3196,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -3227,6 +3257,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -3283,6 +3318,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -3339,6 +3379,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -3395,6 +3440,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -3451,6 +3501,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -3507,6 +3562,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M16" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="34" t="inlineStr">
@@ -3563,6 +3623,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>LC540, Ajhai, LC535, Vrindavan Road</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="34" t="inlineStr">
@@ -3619,6 +3684,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>LC540, Ajhai, LC535, Vrindavan Road</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="34" t="inlineStr">
@@ -3675,6 +3745,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>LC540, Ajhai, LC535, Vrindavan Road</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="34" t="inlineStr">
@@ -3731,6 +3806,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>LC540, Ajhai, LC535, Vrindavan Road</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="34" t="inlineStr">
@@ -3787,6 +3867,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>LC540, Ajhai, LC535, Vrindavan Road</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -3843,6 +3928,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
@@ -3899,6 +3989,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -3955,6 +4050,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="34" t="inlineStr">
@@ -4011,6 +4111,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>LC540, Ajhai, LC535, Vrindavan Road</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="34" t="inlineStr">
@@ -4067,6 +4172,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M26" s="16" t="inlineStr">
+        <is>
+          <t>LC540, Ajhai, LC535, Vrindavan Road</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -4123,6 +4233,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
@@ -4179,6 +4294,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -4235,6 +4355,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
@@ -4291,6 +4416,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -4347,6 +4477,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
@@ -4403,6 +4538,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -4459,6 +4599,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
@@ -4515,6 +4660,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -4571,6 +4721,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
@@ -4627,6 +4782,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -4683,6 +4843,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -4739,6 +4904,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
@@ -4795,6 +4965,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M39" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -4851,6 +5026,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M40" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
@@ -4907,6 +5087,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M41" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
@@ -4963,6 +5148,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
@@ -5019,6 +5209,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M43" s="16" t="inlineStr">
+        <is>
+          <t>LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
@@ -5075,6 +5270,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
@@ -5131,6 +5331,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M45" s="16" t="inlineStr">
+        <is>
+          <t>LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -5187,6 +5392,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M46" s="16" t="inlineStr">
+        <is>
+          <t>LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -5243,6 +5453,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M47" s="16" t="inlineStr">
+        <is>
+          <t>LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
@@ -5299,6 +5514,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M48" s="16" t="inlineStr">
+        <is>
+          <t>LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
@@ -5355,6 +5575,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M49" s="16" t="inlineStr">
+        <is>
+          <t>LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
@@ -5411,6 +5636,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M50" s="16" t="inlineStr">
+        <is>
+          <t>LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
@@ -5467,6 +5697,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M51" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
@@ -5523,6 +5758,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M52" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
@@ -5579,6 +5819,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
@@ -5633,6 +5878,11 @@
       <c r="L54" s="16" t="inlineStr">
         <is>
           <t>Valid</t>
+        </is>
+      </c>
+      <c r="M54" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
         </is>
       </c>
     </row>
